--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F900"/>
+  <dimension ref="A1:F920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24970,7 +24970,11 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B829" t="inlineStr"/>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
       <c r="C829" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25474,7 +25478,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B847" t="inlineStr"/>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C847" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -25490,7 +25498,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B848" t="inlineStr"/>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C848" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25506,7 +25518,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B849" t="inlineStr"/>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C849" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -25522,7 +25538,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B850" t="inlineStr"/>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C850" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -25538,7 +25558,11 @@
           <t>DM-9519034/2026</t>
         </is>
       </c>
-      <c r="B851" t="inlineStr"/>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25554,7 +25578,11 @@
           <t>DC-9519020/2026</t>
         </is>
       </c>
-      <c r="B852" t="inlineStr"/>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>9519020</t>
+        </is>
+      </c>
       <c r="C852" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25602,7 +25630,11 @@
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B854" t="inlineStr"/>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
       <c r="C854" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25626,7 +25658,11 @@
           <t>DC-9519295/2026</t>
         </is>
       </c>
-      <c r="B855" t="inlineStr"/>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C855" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25650,7 +25686,11 @@
           <t>DC-9519295/2026</t>
         </is>
       </c>
-      <c r="B856" t="inlineStr"/>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C856" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25674,7 +25714,11 @@
           <t>DC-9518140/2026</t>
         </is>
       </c>
-      <c r="B857" t="inlineStr"/>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
       <c r="C857" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25698,7 +25742,11 @@
           <t>DC-9518140/2026</t>
         </is>
       </c>
-      <c r="B858" t="inlineStr"/>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
       <c r="C858" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25754,7 +25802,11 @@
           <t>DM-007/2024-A</t>
         </is>
       </c>
-      <c r="B860" t="inlineStr"/>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>9422060</t>
+        </is>
+      </c>
       <c r="C860" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25854,12 +25906,12 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
@@ -25886,12 +25938,12 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
@@ -25913,17 +25965,17 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -25945,17 +25997,17 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -25977,17 +26029,17 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
@@ -26009,17 +26061,17 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
@@ -26031,74 +26083,110 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B870" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C870" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr"/>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>-17.21201508102213</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B871" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B872" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C872" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26106,25 +26194,29 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26134,29 +26226,29 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26166,27 +26258,31 @@
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B875" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C875" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26194,25 +26290,29 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F875" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -26222,61 +26322,57 @@
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>-42.91331545001727</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26286,43 +26382,47 @@
       </c>
       <c r="D878" t="inlineStr"/>
       <c r="E878" t="inlineStr"/>
-      <c r="F878" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="F878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>-21.23264738347681</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr"/>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>9515457</t>
+        </is>
+      </c>
       <c r="C880" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26330,12 +26430,12 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>-19.2091689</t>
+          <t>-21.23528484003703</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>-44.24819679999999</t>
+          <t>-43.44604111152106</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -26343,10 +26443,14 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr"/>
+          <t>DO-009482017/2025-L3</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>9482017</t>
+        </is>
+      </c>
       <c r="C881" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26354,25 +26458,29 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>-19.347297668442856</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>-44.17816254149293</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -26380,23 +26488,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D882" t="inlineStr"/>
-      <c r="E882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26406,27 +26522,27 @@
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>-19.7469167</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>-47.9483714</t>
-        </is>
-      </c>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B884" t="inlineStr"/>
+          <t>DO-9481987/2025-L7</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>9481987</t>
+        </is>
+      </c>
       <c r="C884" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26434,23 +26550,31 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
-        </is>
-      </c>
-      <c r="F884" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B885" t="inlineStr"/>
+          <t>DO-009482055/2025-L5</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>9482055</t>
+        </is>
+      </c>
       <c r="C885" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26458,23 +26582,31 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
-      <c r="F885" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B886" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C886" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26482,63 +26614,71 @@
       </c>
       <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr"/>
-      <c r="F886" t="inlineStr"/>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
-        </is>
-      </c>
-      <c r="B887" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C887" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>-22.087663382295393</t>
-        </is>
-      </c>
-      <c r="E887" t="inlineStr">
-        <is>
-          <t>-46.558100143637475</t>
-        </is>
-      </c>
-      <c r="F887" t="inlineStr"/>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C888" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>-22.047693352827803</t>
-        </is>
-      </c>
-      <c r="E888" t="inlineStr">
-        <is>
-          <t>-46.555137035221186</t>
-        </is>
-      </c>
-      <c r="F888" t="inlineStr"/>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B889" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C889" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26546,7 +26686,11 @@
       </c>
       <c r="D889" t="inlineStr"/>
       <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr"/>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -26599,12 +26743,12 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -26612,31 +26756,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E892" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr"/>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -26644,29 +26780,25 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E893" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr"/>
+          <t>DC-9519595/2026</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C894" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26674,12 +26806,12 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.2091689</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-44.24819679999999</t>
         </is>
       </c>
       <c r="F894" t="inlineStr"/>
@@ -26687,10 +26819,14 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B895" t="inlineStr"/>
+          <t>DC-9519595/2026</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C895" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26698,12 +26834,12 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>-16.964100809511475</t>
+          <t>-19.347297668442856</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>-46.40676935458991</t>
+          <t>-44.17816254149293</t>
         </is>
       </c>
       <c r="F895" t="inlineStr"/>
@@ -26711,36 +26847,36 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B896" t="inlineStr"/>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>9497685</t>
+        </is>
+      </c>
       <c r="C896" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>-16.985130778257258</t>
-        </is>
-      </c>
-      <c r="E896" t="inlineStr">
-        <is>
-          <t>-46.27544298436485</t>
-        </is>
-      </c>
-      <c r="F896" t="inlineStr"/>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2301762 000023/2025</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -26750,12 +26886,12 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-19.7469167</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>-44.943418</t>
+          <t>-47.9483714</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
@@ -26767,12 +26903,12 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -26780,23 +26916,27 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D898" t="inlineStr"/>
-      <c r="E898" t="inlineStr"/>
-      <c r="F898" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>-15.483562</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>-44.39677500000001</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -26804,23 +26944,27 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D899" t="inlineStr"/>
-      <c r="E899" t="inlineStr"/>
-      <c r="F899" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>-15.5007309</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>-44.7624674</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -26830,7 +26974,519 @@
       </c>
       <c r="D900" t="inlineStr"/>
       <c r="E900" t="inlineStr"/>
-      <c r="F900" t="inlineStr">
+      <c r="F900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>DC-9519740/2026</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>9519740</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>-22.087663382295393</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>-46.558100143637475</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>DC-9519740/2026</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>9519740</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>-22.047693352827803</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>-46.555137035221186</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr"/>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr"/>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr"/>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr"/>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr"/>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>-16.964100809511475</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>-46.40676935458991</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>-16.985130778257258</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>-46.27544298436485</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F926"/>
+  <dimension ref="A1:F932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -24928,7 +24928,7 @@
       <c r="E827" t="inlineStr"/>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
@@ -25002,7 +25002,11 @@
           <t>DO-009482032/2025-L6</t>
         </is>
       </c>
-      <c r="B830" t="inlineStr"/>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>9482032</t>
+        </is>
+      </c>
       <c r="C830" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25018,7 +25022,11 @@
           <t>-43.983052</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr"/>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -25492,7 +25500,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25512,7 +25520,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25532,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25544,7 +25552,7 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
@@ -25615,12 +25623,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9521130/2026</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9521130</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25628,23 +25636,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
-      <c r="E850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-22.047693352827803</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-46.555137035221186</t>
+        </is>
+      </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301520 000006/2026</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DOV-003/2021-C</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -25652,23 +25668,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-22.087663382295393</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-46.558100143637475</t>
+        </is>
+      </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9521130/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9521130</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25676,31 +25700,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000006/2026</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DOV-003/2021-C</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25708,31 +25724,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25759,12 +25767,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25772,23 +25780,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr"/>
-      <c r="E855" t="inlineStr"/>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25796,23 +25812,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25820,83 +25844,67 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>-21.1994491</t>
-        </is>
-      </c>
-      <c r="E857" t="inlineStr">
-        <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>-21.27464910003665</t>
-        </is>
-      </c>
-      <c r="E858" t="inlineStr">
-        <is>
-          <t>-42.91331545001727</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
@@ -25913,17 +25921,17 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
+          <t>-42.91331545001727</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
@@ -25935,44 +25943,44 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9519020</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>-19.6107675</t>
+          <t>-21.23264738347681</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>-42.64891799999999</t>
+          <t>-43.43361939286979</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25982,29 +25990,29 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>-16.964100809511475</t>
+          <t>-21.23528484003703</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>-46.40676935458991</t>
+          <t>-43.44604111152106</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -26014,29 +26022,29 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-16.985130778257258</t>
+          <t>-19.6107675</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-46.27544298436485</t>
+          <t>-42.64891799999999</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DOV-004/2021-C</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -26046,29 +26054,29 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-16.964100809511475</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-46.40676935458991</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DOV-001/2021-C</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -26078,29 +26086,29 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-16.985130778257258</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-46.27544298436485</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DOV-002/2021-C</t>
+          <t>DOV-004/2021-C</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26108,47 +26116,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
-      <c r="E866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DOV-001/2021-C</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DOV-002/2021-C</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26156,55 +26180,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E868" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26212,23 +26228,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26236,31 +26260,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26279,12 +26295,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26292,8 +26308,16 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F873" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
@@ -26303,10 +26327,14 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B874" t="inlineStr"/>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
       <c r="C874" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26314,17 +26342,21 @@
       </c>
       <c r="D874" t="inlineStr"/>
       <c r="E874" t="inlineStr"/>
-      <c r="F874" t="inlineStr"/>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26336,51 +26368,35 @@
       <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr">
-        <is>
-          <t>9512043</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr"/>
       <c r="C876" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E876" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>2301762 000004/2026</t>
-        </is>
-      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -26388,31 +26404,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
       <c r="F877" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DM-9521156/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9521156</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26420,23 +26428,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr"/>
-      <c r="E878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DM-9521185/2026</t>
+          <t>DPEI-9520827/2026</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>9521185</t>
+          <t>9520827</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -26444,23 +26460,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>-16.7204212</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>-43.8540892</t>
+        </is>
+      </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>2301762 000002/2026</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DM-9521160/2026</t>
+          <t>DPEI-9520825/2026</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>9521160</t>
+          <t>9520825</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -26470,29 +26494,29 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>-16.1675626</t>
+          <t>-18.5966758</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>-42.299072</t>
+          <t>-46.5180885</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -26500,23 +26524,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DM-9521156/2026</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9521156</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -26528,19 +26560,19 @@
       <c r="E882" t="inlineStr"/>
       <c r="F882" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-9437231-A</t>
+          <t>DM-9521185/2026</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9521185</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26552,19 +26584,19 @@
       <c r="E883" t="inlineStr"/>
       <c r="F883" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301762 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
+          <t>DM-9521160/2026</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9521160</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -26574,29 +26606,29 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>-19.0966327</t>
+          <t>-16.1675626</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>-46.67356590000001</t>
+          <t>-42.299072</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26604,31 +26636,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>-19.071165</t>
-        </is>
-      </c>
-      <c r="E885" t="inlineStr">
-        <is>
-          <t>-46.794155</t>
-        </is>
-      </c>
+      <c r="D885" t="inlineStr"/>
+      <c r="E885" t="inlineStr"/>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9518140</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26636,31 +26660,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>-20.011794067707264</t>
-        </is>
-      </c>
-      <c r="E886" t="inlineStr">
-        <is>
-          <t>-44.21840097426832</t>
-        </is>
-      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
       <c r="F886" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
+          <t>DM-9437231-A</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9518140</t>
+          <t>9437231</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26668,31 +26684,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>-20.051632324197044</t>
-        </is>
-      </c>
-      <c r="E887" t="inlineStr">
-        <is>
-          <t>-44.19399735422576</t>
-        </is>
-      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301762 000006/2024</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>VD - 9513695/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9513695</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -26702,29 +26710,29 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>-19.7852937</t>
+          <t>-19.0966327</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>-43.95059879999999</t>
+          <t>-46.67356590000001</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DM-9521162/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9521162</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26732,23 +26740,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>-19.071165</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>-46.794155</t>
+        </is>
+      </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -26756,23 +26772,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr"/>
-      <c r="E890" t="inlineStr"/>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>-20.011794067707264</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>-44.21840097426832</t>
+        </is>
+      </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -26780,23 +26804,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr"/>
-      <c r="E891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>-20.051632324197044</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>-44.19399735422576</t>
+        </is>
+      </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>VD - 9513687/2026</t>
+          <t>VD - 9513695/2026</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9513687</t>
+          <t>9513695</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -26823,12 +26855,12 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>VD-9513684/2026</t>
+          <t>DM-9521162/2026</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9513684</t>
+          <t>9521162</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -26836,31 +26868,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>-21.5802619</t>
-        </is>
-      </c>
-      <c r="E893" t="inlineStr">
-        <is>
-          <t>-45.4432806</t>
-        </is>
-      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>VD-9513684/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>9513684</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -26868,16 +26892,8 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D894" t="inlineStr">
-        <is>
-          <t>-19.7852937</t>
-        </is>
-      </c>
-      <c r="E894" t="inlineStr">
-        <is>
-          <t>-43.95059879999999</t>
-        </is>
-      </c>
+      <c r="D894" t="inlineStr"/>
+      <c r="E894" t="inlineStr"/>
       <c r="F894" t="inlineStr">
         <is>
           <t>2301001 000001/2026</t>
@@ -26887,12 +26903,12 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DC-9518767/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>9518767</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -26900,31 +26916,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>-21.4612859</t>
-        </is>
-      </c>
-      <c r="E895" t="inlineStr">
-        <is>
-          <t>-44.1581764</t>
-        </is>
-      </c>
+      <c r="D895" t="inlineStr"/>
+      <c r="E895" t="inlineStr"/>
       <c r="F895" t="inlineStr">
         <is>
-          <t>1301606 000001/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>DM-9521166/2026</t>
+          <t>VD - 9513687/2026</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>9521166</t>
+          <t>9513687</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -26934,29 +26942,29 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>-16.2162402</t>
+          <t>-19.7852937</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>-44.4336888</t>
+          <t>-43.95059879999999</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>DM-9521157/2026</t>
+          <t>VD-9513684/2026</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>9521157</t>
+          <t>9513684</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -26966,29 +26974,29 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>-15.8071355</t>
+          <t>-21.5802619</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>-43.3007305</t>
+          <t>-45.4432806</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
+          <t>VD-9513684/2026</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>9512044</t>
+          <t>9513684</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -26996,55 +27004,59 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D898" t="inlineStr"/>
-      <c r="E898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>-19.7852937</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>-43.95059879999999</t>
+        </is>
+      </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9518767/2026</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9518767</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-21.4612859</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
-      <c r="F899" t="inlineStr">
-        <is>
-          <t>2301901 000003/2021</t>
-        </is>
-      </c>
+          <t>-44.1581764</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>DM-9521171/2026</t>
+          <t>DM-9521166/2026</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>9521171</t>
+          <t>9521166</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -27054,12 +27066,12 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>-16.7204212</t>
+          <t>-16.2162402</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>-43.8540892</t>
+          <t>-44.4336888</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
@@ -27071,12 +27083,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>DM-9521173/2026</t>
+          <t>DM-9521157/2026</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>9521173</t>
+          <t>9521157</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -27084,8 +27096,16 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D901" t="inlineStr"/>
-      <c r="E901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>-15.8071355</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>-43.3007305</t>
+        </is>
+      </c>
       <c r="F901" t="inlineStr">
         <is>
           <t>2301762 000011/2026</t>
@@ -27095,12 +27115,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>DM-9521564/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>9521564</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -27112,43 +27132,51 @@
       <c r="E902" t="inlineStr"/>
       <c r="F902" t="inlineStr">
         <is>
-          <t>2301762 000010/2026</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D903" t="inlineStr"/>
-      <c r="E903" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -27158,29 +27186,29 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-16.7204212</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-43.8540892</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -27190,29 +27218,29 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-16.7204212</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-43.8540892</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-9521173/2026</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9521173</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -27220,31 +27248,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E906" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
       <c r="F906" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9521564/2026</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9521564</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -27252,31 +27272,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E907" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
       <c r="F907" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000010/2026</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>DM-9521426/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>9521426</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -27284,31 +27296,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>-21.1979015</t>
-        </is>
-      </c>
-      <c r="E908" t="inlineStr">
-        <is>
-          <t>-43.7837369</t>
-        </is>
-      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
       <c r="F908" t="inlineStr">
         <is>
-          <t>2301762 000009/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -27316,23 +27320,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D909" t="inlineStr"/>
-      <c r="E909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -27340,55 +27352,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D910" t="inlineStr"/>
-      <c r="E910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -27398,61 +27418,61 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9521426/2026</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9521426</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-21.1979015</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.7837369</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000009/2026</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -27464,19 +27484,19 @@
       <c r="E914" t="inlineStr"/>
       <c r="F914" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -27488,43 +27508,51 @@
       <c r="E915" t="inlineStr"/>
       <c r="F915" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D916" t="inlineStr"/>
-      <c r="E916" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -27532,47 +27560,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D917" t="inlineStr"/>
-      <c r="E917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D918" t="inlineStr"/>
-      <c r="E918" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -27580,31 +27624,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D919" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E919" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
       <c r="F919" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -27612,55 +27648,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D920" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E920" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
       <c r="F920" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr"/>
       <c r="F921" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -27672,67 +27700,75 @@
       <c r="E922" t="inlineStr"/>
       <c r="F922" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D923" t="inlineStr"/>
       <c r="E923" t="inlineStr"/>
       <c r="F923" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D924" t="inlineStr"/>
-      <c r="E924" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>9519034</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -27740,43 +27776,195 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D925" t="inlineStr"/>
-      <c r="E925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr"/>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr"/>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr"/>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr"/>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr"/>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B926" t="inlineStr">
+      <c r="B931" t="inlineStr">
         <is>
           <t>9519017</t>
         </is>
       </c>
-      <c r="C926" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D926" t="inlineStr">
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
         <is>
           <t>-18.46005275010656</t>
         </is>
       </c>
-      <c r="E926" t="inlineStr">
+      <c r="E931" t="inlineStr">
         <is>
           <t>-48.18218127247928</t>
         </is>
       </c>
-      <c r="F926" t="inlineStr">
+      <c r="F931" t="inlineStr">
         <is>
           <t>2301520 000017/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>DPEI-9520716/2026</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>9520716</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr"/>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2301601 000007/2026</t>
         </is>
       </c>
     </row>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F932"/>
+  <dimension ref="A1:F937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23111,10 +23111,14 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr"/>
+          <t>AEST-9469794/2025</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>9469794</t>
+        </is>
+      </c>
       <c r="C764" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23122,7 +23126,11 @@
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr"/>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2301931 000002/2025</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -24007,10 +24015,14 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-9441355/2024 </t>
-        </is>
-      </c>
-      <c r="B795" t="inlineStr"/>
+          <t>DC-9441355/2024</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>9441355</t>
+        </is>
+      </c>
       <c r="C795" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -24026,7 +24038,11 @@
           <t>-41.506751</t>
         </is>
       </c>
-      <c r="F795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>2301520 000014/2024</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -25004,7 +25020,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -25230,12 +25246,12 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25289,17 +25305,17 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25321,17 +25337,17 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25358,12 +25374,12 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25390,12 +25406,12 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -25407,12 +25423,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -25420,23 +25436,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr"/>
-      <c r="E843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>-17.21201508102213</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -25446,29 +25470,29 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25478,29 +25502,29 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9519595</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25510,29 +25534,29 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-19.2091689</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-44.24819679999999</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301520 000037/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9519595</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25540,31 +25564,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>-19.347297668442856</t>
-        </is>
-      </c>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>-44.17816254149293</t>
-        </is>
-      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301520 000037/2026</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25574,29 +25590,29 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-22.087663382295393</t>
+          <t>-15.483562</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>-46.558100143637475</t>
+          <t>-44.39677500000001</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25606,29 +25622,29 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-22.047693352827803</t>
+          <t>-15.5007309</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>-46.555137035221186</t>
+          <t>-44.7624674</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25638,29 +25654,29 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>-22.047693352827803</t>
+          <t>-19.2091689</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>-46.555137035221186</t>
+          <t>-44.24819679999999</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -25670,29 +25686,29 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>-22.087663382295393</t>
+          <t>-19.347297668442856</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>-46.558100143637475</t>
+          <t>-44.17816254149293</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DC-9521130/2026</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9521130</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25700,23 +25716,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
-      <c r="E852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-22.087663382295393</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-46.558100143637475</t>
+        </is>
+      </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301520 000006/2026</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DOV-003/2021-C</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -25724,23 +25748,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr"/>
-      <c r="E853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>-22.047693352827803</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>-46.555137035221186</t>
+        </is>
+      </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -25750,29 +25782,29 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-22.047693352827803</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.555137035221186</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25782,29 +25814,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-22.087663382295393</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.558100143637475</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9521130/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9521130</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25812,31 +25844,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000006/2026</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DOV-003/2021-C</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25848,19 +25872,19 @@
       <c r="E857" t="inlineStr"/>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25868,23 +25892,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25894,93 +25926,85 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D861" t="inlineStr">
-        <is>
-          <t>-21.23264738347681</t>
-        </is>
-      </c>
-      <c r="E861" t="inlineStr">
-        <is>
-          <t>-43.43361939286979</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr"/>
+      <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25988,31 +26012,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>-21.23528484003703</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9519020</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -26022,93 +26038,93 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-19.6107675</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-42.64891799999999</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-16.964100809511475</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-46.40676935458991</t>
+          <t>-42.91331545001727</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-16.985130778257258</t>
+          <t>-21.23264738347681</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-46.27544298436485</t>
+          <t>-43.43361939286979</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DOV-004/2021-C</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26118,29 +26134,29 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-21.23528484003703</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-43.44604111152106</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DOV-001/2021-C</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26150,29 +26166,29 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.6107675</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-42.64891799999999</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DOV-002/2021-C</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9292040</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26180,47 +26196,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-16.964100809511475</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-46.40676935458991</t>
+        </is>
+      </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>-16.985130778257258</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-46.27544298436485</t>
+        </is>
+      </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DOV-004/2021-C</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26230,29 +26262,29 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DOV-001/2021-C</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26260,23 +26292,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DOV-002/2021-C</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26288,51 +26328,43 @@
       <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D873" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E873" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26340,23 +26372,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
-      <c r="E874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26368,17 +26408,21 @@
       <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr"/>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
       <c r="C876" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26386,17 +26430,21 @@
       </c>
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -26404,23 +26452,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr"/>
-      <c r="E877" t="inlineStr"/>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26428,31 +26484,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DPEI-9520827/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>9520827</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -26460,31 +26508,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>-16.7204212</t>
-        </is>
-      </c>
-      <c r="E879" t="inlineStr">
-        <is>
-          <t>-43.8540892</t>
-        </is>
-      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
       <c r="F879" t="inlineStr">
         <is>
-          <t>2301601 000001/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DPEI-9520825/2026</t>
+          <t>AMA-9502187/2026</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>9520825</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -26492,31 +26532,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>-18.5966758</t>
-        </is>
-      </c>
-      <c r="E880" t="inlineStr">
-        <is>
-          <t>-46.5180885</t>
-        </is>
-      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
       <c r="F880" t="inlineStr">
         <is>
-          <t>2301601 000001/2026</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>AMA-9502187/2026</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -26524,31 +26556,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E881" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
       <c r="F881" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DM-9521156/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9521156</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -26560,19 +26584,19 @@
       <c r="E882" t="inlineStr"/>
       <c r="F882" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-9521185/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9521185</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26580,23 +26604,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D883" t="inlineStr"/>
-      <c r="E883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>2301762 000002/2026</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DM-9521160/2026</t>
+          <t>DPEI-9520827/2026</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9521160</t>
+          <t>9520827</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -26606,29 +26638,29 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>-16.1675626</t>
+          <t>-16.7204212</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>-42.299072</t>
+          <t>-43.8540892</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DPEI-9520825/2026</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9520825</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26636,23 +26668,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D885" t="inlineStr"/>
-      <c r="E885" t="inlineStr"/>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>-18.5966758</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>-46.5180885</t>
+        </is>
+      </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26660,23 +26700,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr"/>
-      <c r="E886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DM-9437231-A</t>
+          <t>DM-9521156/2026</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9521156</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26688,19 +26736,19 @@
       <c r="E887" t="inlineStr"/>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
+          <t>DM-9521185/2026</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9521185</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -26708,31 +26756,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>-19.0966327</t>
-        </is>
-      </c>
-      <c r="E888" t="inlineStr">
-        <is>
-          <t>-46.67356590000001</t>
-        </is>
-      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301762 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
+          <t>DM-9521160/2026</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9521160</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26742,29 +26782,29 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>-19.071165</t>
+          <t>-16.1675626</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>-46.794155</t>
+          <t>-42.299072</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9518140</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -26772,31 +26812,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t>-20.011794067707264</t>
-        </is>
-      </c>
-      <c r="E890" t="inlineStr">
-        <is>
-          <t>-44.21840097426832</t>
-        </is>
-      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
       <c r="F890" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9518140</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -26804,31 +26836,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>-20.051632324197044</t>
-        </is>
-      </c>
-      <c r="E891" t="inlineStr">
-        <is>
-          <t>-44.19399735422576</t>
-        </is>
-      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
       <c r="F891" t="inlineStr">
         <is>
-          <t>2301520 000007/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>VD - 9513695/2026</t>
+          <t>DM-9437231-A</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9513695</t>
+          <t>9437231</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -26836,31 +26860,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>-19.7852937</t>
-        </is>
-      </c>
-      <c r="E892" t="inlineStr">
-        <is>
-          <t>-43.95059879999999</t>
-        </is>
-      </c>
+      <c r="D892" t="inlineStr"/>
+      <c r="E892" t="inlineStr"/>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000006/2024</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>DM-9521162/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9521162</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -26868,23 +26884,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr"/>
-      <c r="E893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>-19.0966327</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>-46.67356590000001</t>
+        </is>
+      </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -26892,23 +26916,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D894" t="inlineStr"/>
-      <c r="E894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>-19.071165</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>-46.794155</t>
+        </is>
+      </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -26916,23 +26948,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr"/>
-      <c r="E895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>-20.011794067707264</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>-44.21840097426832</t>
+        </is>
+      </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>VD - 9513687/2026</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>9513687</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -26942,29 +26982,29 @@
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>-19.7852937</t>
+          <t>-20.051632324197044</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>-43.95059879999999</t>
+          <t>-44.19399735422576</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>VD-9513684/2026</t>
+          <t>VD - 9513695/2026</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>9513684</t>
+          <t>9513695</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -26974,12 +27014,12 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>-21.5802619</t>
+          <t>-19.7852937</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>-45.4432806</t>
+          <t>-43.95059879999999</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
@@ -26991,12 +27031,12 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>VD-9513684/2026</t>
+          <t>DM-9521162/2026</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>9513684</t>
+          <t>9521162</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -27004,31 +27044,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>-19.7852937</t>
-        </is>
-      </c>
-      <c r="E898" t="inlineStr">
-        <is>
-          <t>-43.95059879999999</t>
-        </is>
-      </c>
+      <c r="D898" t="inlineStr"/>
+      <c r="E898" t="inlineStr"/>
       <c r="F898" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>DC-9518767/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>9518767</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -27036,27 +27068,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>-21.4612859</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>-44.1581764</t>
-        </is>
-      </c>
-      <c r="F899" t="inlineStr"/>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2301001 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>DM-9521166/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>9521166</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -27064,31 +27092,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>-16.2162402</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>-44.4336888</t>
-        </is>
-      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
       <c r="F900" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>DM-9521157/2026</t>
+          <t>VD - 9513687/2026</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>9521157</t>
+          <t>9513687</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -27098,29 +27118,29 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>-15.8071355</t>
+          <t>-19.7852937</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>-43.3007305</t>
+          <t>-43.95059879999999</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
+          <t>VD-9513684/2026</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>9512044</t>
+          <t>9513684</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -27128,55 +27148,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D902" t="inlineStr"/>
-      <c r="E902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>-21.5802619</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>-45.4432806</t>
+        </is>
+      </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>VD-9513684/2026</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9513684</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.7852937</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-43.95059879999999</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>DM-9521171/2026</t>
+          <t>DC-9518767/2026</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>9521171</t>
+          <t>9518767</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -27186,29 +27214,29 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>-16.7204212</t>
+          <t>-21.4612859</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>-43.8540892</t>
+          <t>-44.1581764</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>2301762 000011/2026</t>
+          <t>1301606 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>DM-9521171/2026</t>
+          <t>DM-9521166/2026</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>9521171</t>
+          <t>9521166</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -27218,12 +27246,12 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>-16.7204212</t>
+          <t>-16.2162402</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>-43.8540892</t>
+          <t>-44.4336888</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
@@ -27235,12 +27263,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>DM-9521173/2026</t>
+          <t>DM-9521157/2026</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>9521173</t>
+          <t>9521157</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -27248,8 +27276,16 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr"/>
-      <c r="E906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>-15.8071355</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>-43.3007305</t>
+        </is>
+      </c>
       <c r="F906" t="inlineStr">
         <is>
           <t>2301762 000011/2026</t>
@@ -27259,12 +27295,12 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>DM-9521564/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>9521564</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -27276,43 +27312,51 @@
       <c r="E907" t="inlineStr"/>
       <c r="F907" t="inlineStr">
         <is>
-          <t>2301762 000010/2026</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D908" t="inlineStr"/>
-      <c r="E908" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -27322,29 +27366,29 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-16.7204212</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-43.8540892</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -27354,29 +27398,29 @@
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-16.7204212</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-43.8540892</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-9521173/2026</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9521173</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -27384,31 +27428,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E911" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
       <c r="F911" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9521564/2026</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9521564</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -27416,31 +27452,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E912" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D912" t="inlineStr"/>
+      <c r="E912" t="inlineStr"/>
       <c r="F912" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000010/2026</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>DM-9521426/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>9521426</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -27448,31 +27476,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>-21.1979015</t>
-        </is>
-      </c>
-      <c r="E913" t="inlineStr">
-        <is>
-          <t>-43.7837369</t>
-        </is>
-      </c>
+      <c r="D913" t="inlineStr"/>
+      <c r="E913" t="inlineStr"/>
       <c r="F913" t="inlineStr">
         <is>
-          <t>2301762 000009/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -27480,23 +27500,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D914" t="inlineStr"/>
-      <c r="E914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -27504,55 +27532,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D915" t="inlineStr"/>
-      <c r="E915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -27562,61 +27598,61 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9521426/2026</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9521426</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-21.1979015</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.7837369</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000009/2026</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -27628,19 +27664,19 @@
       <c r="E919" t="inlineStr"/>
       <c r="F919" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -27652,43 +27688,51 @@
       <c r="E920" t="inlineStr"/>
       <c r="F920" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D921" t="inlineStr"/>
-      <c r="E921" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -27696,47 +27740,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D922" t="inlineStr"/>
-      <c r="E922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D923" t="inlineStr"/>
-      <c r="E923" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -27744,31 +27804,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D924" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E924" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D924" t="inlineStr"/>
+      <c r="E924" t="inlineStr"/>
       <c r="F924" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -27776,55 +27828,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D925" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E925" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
       <c r="F925" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr"/>
       <c r="F926" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -27836,67 +27880,75 @@
       <c r="E927" t="inlineStr"/>
       <c r="F927" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr"/>
       <c r="F928" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D929" t="inlineStr"/>
-      <c r="E929" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>9519034</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -27904,55 +27956,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D930" t="inlineStr"/>
-      <c r="E930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>DC-9519017/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>9519017</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D931" t="inlineStr">
-        <is>
-          <t>-18.46005275010656</t>
-        </is>
-      </c>
-      <c r="E931" t="inlineStr">
-        <is>
-          <t>-48.18218127247928</t>
-        </is>
-      </c>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
       <c r="F931" t="inlineStr">
         <is>
-          <t>2301520 000017/2026</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>DPEI-9520716/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>9520716</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -27963,6 +28015,134 @@
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr"/>
       <c r="F932" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr"/>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr"/>
+      <c r="E934" t="inlineStr"/>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr"/>
+      <c r="E935" t="inlineStr"/>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>DC-9519017/2026</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>-18.46005275010656</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>-48.18218127247928</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2301520 000017/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>DPEI-9520716/2026</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>9520716</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
         <is>
           <t>2301601 000007/2026</t>
         </is>
